--- a/data/trans_orig/P19C10_2023-Clase-trans_orig.xlsx
+++ b/data/trans_orig/P19C10_2023-Clase-trans_orig.xlsx
@@ -535,7 +535,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según si el motivo por su última visita al dentista fue por dolor de mandíbula / solo 2023 en 2023</t>
+          <t>Población según si el motivo por su última visita al dentista fue por dolor de mandíbula / solo 2023 en 2023 (tasa de respuesta: 99,54%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -735,7 +735,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>5696</t>
+          <t>6420</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -750,7 +750,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>1,14%</t>
+          <t>1,29%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -765,12 +765,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>778</t>
+          <t>1066</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>8360</t>
+          <t>8678</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -780,12 +780,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>0,18%</t>
+          <t>0,24%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>1,9%</t>
+          <t>1,97%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -800,12 +800,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>1712</t>
+          <t>1433</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>11152</t>
+          <t>10294</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -815,12 +815,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>0,18%</t>
+          <t>0,15%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>1,19%</t>
+          <t>1,1%</t>
         </is>
       </c>
     </row>
@@ -843,7 +843,7 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>492786</t>
+          <t>492062</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -858,7 +858,7 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>98,86%</t>
+          <t>98,71%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -878,12 +878,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>432565</t>
+          <t>432247</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>440147</t>
+          <t>439859</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -893,12 +893,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>98,1%</t>
+          <t>98,03%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>99,82%</t>
+          <t>99,76%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -913,12 +913,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>928255</t>
+          <t>929113</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>937695</t>
+          <t>937974</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -928,12 +928,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>98,81%</t>
+          <t>98,9%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>99,82%</t>
+          <t>99,85%</t>
         </is>
       </c>
     </row>
@@ -1078,7 +1078,7 @@
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>5483</t>
+          <t>6580</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1093,7 +1093,7 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>1,22%</t>
+          <t>1,47%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1108,12 +1108,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>907</t>
+          <t>1027</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>8144</t>
+          <t>7343</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1123,12 +1123,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>0,24%</t>
+          <t>0,27%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>2,16%</t>
+          <t>1,94%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1143,12 +1143,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>1519</t>
+          <t>1394</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>9922</t>
+          <t>9925</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1158,7 +1158,7 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>0,18%</t>
+          <t>0,17%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
@@ -1186,7 +1186,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>442935</t>
+          <t>441838</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -1201,7 +1201,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>98,78%</t>
+          <t>98,53%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -1221,12 +1221,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>369462</t>
+          <t>370263</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>376699</t>
+          <t>376579</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1236,12 +1236,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>97,84%</t>
+          <t>98,06%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>99,76%</t>
+          <t>99,73%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1256,12 +1256,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>816101</t>
+          <t>816098</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>824504</t>
+          <t>824629</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1276,7 +1276,7 @@
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>99,82%</t>
+          <t>99,83%</t>
         </is>
       </c>
     </row>
@@ -1421,7 +1421,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>8804</t>
+          <t>9285</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1436,7 +1436,7 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>1,33%</t>
+          <t>1,41%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1451,12 +1451,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>1187</t>
+          <t>1105</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>8697</t>
+          <t>8016</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1466,12 +1466,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>0,72%</t>
+          <t>0,67%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>5,27%</t>
+          <t>4,86%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1486,12 +1486,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>1347</t>
+          <t>1340</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>12692</t>
+          <t>13816</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1506,7 +1506,7 @@
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>1,54%</t>
+          <t>1,67%</t>
         </is>
       </c>
     </row>
@@ -1529,7 +1529,7 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>651925</t>
+          <t>651444</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
@@ -1544,7 +1544,7 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>98,67%</t>
+          <t>98,59%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
@@ -1564,12 +1564,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>156271</t>
+          <t>156952</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>163781</t>
+          <t>163863</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1579,12 +1579,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>94,73%</t>
+          <t>95,14%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>99,28%</t>
+          <t>99,33%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1599,12 +1599,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>813005</t>
+          <t>811881</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>824350</t>
+          <t>824357</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1614,7 +1614,7 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>98,46%</t>
+          <t>98,33%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
@@ -1764,7 +1764,7 @@
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>3940</t>
+          <t>3487</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1779,7 +1779,7 @@
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>0,39%</t>
+          <t>0,35%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1794,12 +1794,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>114</t>
+          <t>161</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>4590</t>
+          <t>4523</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1809,12 +1809,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>0,01%</t>
+          <t>0,02%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>0,48%</t>
+          <t>0,47%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1829,12 +1829,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>527</t>
+          <t>587</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>5315</t>
+          <t>6175</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1849,7 +1849,7 @@
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>0,27%</t>
+          <t>0,32%</t>
         </is>
       </c>
     </row>
@@ -1872,7 +1872,7 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>994211</t>
+          <t>994664</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
@@ -1887,7 +1887,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>99,61%</t>
+          <t>99,65%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -1907,12 +1907,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>954279</t>
+          <t>954346</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>958755</t>
+          <t>958708</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1922,12 +1922,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>99,52%</t>
+          <t>99,53%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>99,99%</t>
+          <t>99,98%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1942,12 +1942,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1951705</t>
+          <t>1950845</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1956493</t>
+          <t>1956433</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1957,7 +1957,7 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>99,73%</t>
+          <t>99,68%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
@@ -2107,7 +2107,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>6675</t>
+          <t>8260</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2122,7 +2122,7 @@
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>1,52%</t>
+          <t>1,88%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2137,12 +2137,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>1343</t>
+          <t>1657</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>8025</t>
+          <t>7589</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2152,12 +2152,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>0,16%</t>
+          <t>0,2%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>0,99%</t>
+          <t>0,93%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2172,12 +2172,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>2156</t>
+          <t>2366</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>10814</t>
+          <t>10804</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2187,7 +2187,7 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>0,17%</t>
+          <t>0,19%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
@@ -2215,7 +2215,7 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>432177</t>
+          <t>430592</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
@@ -2230,7 +2230,7 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>98,48%</t>
+          <t>98,12%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
@@ -2250,12 +2250,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>805956</t>
+          <t>806392</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>812638</t>
+          <t>812324</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2265,12 +2265,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>99,01%</t>
+          <t>99,07%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>99,84%</t>
+          <t>99,8%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2285,12 +2285,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>1242019</t>
+          <t>1242029</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>1250677</t>
+          <t>1250467</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2305,7 +2305,7 @@
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>99,83%</t>
+          <t>99,81%</t>
         </is>
       </c>
     </row>
@@ -2450,7 +2450,7 @@
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>8512</t>
+          <t>8864</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2465,7 +2465,7 @@
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>3,65%</t>
+          <t>3,8%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2480,12 +2480,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>2554</t>
+          <t>2513</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>10466</t>
+          <t>11013</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2500,7 +2500,7 @@
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>1,41%</t>
+          <t>1,48%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2515,12 +2515,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>3489</t>
+          <t>3398</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>14439</t>
+          <t>14620</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2530,12 +2530,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>0,36%</t>
+          <t>0,35%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>1,48%</t>
+          <t>1,5%</t>
         </is>
       </c>
     </row>
@@ -2558,7 +2558,7 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>224700</t>
+          <t>224348</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
@@ -2573,7 +2573,7 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>96,35%</t>
+          <t>96,2%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
@@ -2593,12 +2593,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>733444</t>
+          <t>732897</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>741356</t>
+          <t>741397</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2608,7 +2608,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>98,59%</t>
+          <t>98,52%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -2628,12 +2628,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>962683</t>
+          <t>962502</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>973633</t>
+          <t>973724</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2643,12 +2643,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>98,52%</t>
+          <t>98,5%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>99,64%</t>
+          <t>99,65%</t>
         </is>
       </c>
     </row>
@@ -2788,12 +2788,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>3416</t>
+          <t>3404</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>17608</t>
+          <t>18031</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2808,7 +2808,7 @@
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>0,54%</t>
+          <t>0,55%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2823,12 +2823,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>13003</t>
+          <t>12775</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>29403</t>
+          <t>28695</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2838,12 +2838,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>0,37%</t>
+          <t>0,36%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>0,84%</t>
+          <t>0,82%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2858,12 +2858,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>19875</t>
+          <t>19801</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>40472</t>
+          <t>40139</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2878,7 +2878,7 @@
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>0,6%</t>
+          <t>0,59%</t>
         </is>
       </c>
     </row>
@@ -2901,12 +2901,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>3260235</t>
+          <t>3259812</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>3274427</t>
+          <t>3274439</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2916,7 +2916,7 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>99,46%</t>
+          <t>99,45%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
@@ -2936,12 +2936,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>3470856</t>
+          <t>3471564</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>3487256</t>
+          <t>3487484</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2951,12 +2951,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>99,16%</t>
+          <t>99,18%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>99,63%</t>
+          <t>99,64%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2971,12 +2971,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>6737630</t>
+          <t>6737963</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>6758227</t>
+          <t>6758301</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2986,7 +2986,7 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>99,4%</t>
+          <t>99,41%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">

--- a/data/trans_orig/P19C10_2023-Clase-trans_orig.xlsx
+++ b/data/trans_orig/P19C10_2023-Clase-trans_orig.xlsx
@@ -725,7 +725,7 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>1133</t>
+          <t>1164</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
@@ -735,12 +735,12 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>6420</t>
+          <t>5888</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>0,23%</t>
+          <t>0,21%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
@@ -750,7 +750,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>1,29%</t>
+          <t>1,09%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -760,32 +760,32 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>3254</t>
+          <t>3330</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>1066</t>
+          <t>833</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>8678</t>
+          <t>8886</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>0,74%</t>
+          <t>0,69%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>0,24%</t>
+          <t>0,17%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>1,97%</t>
+          <t>1,85%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -795,32 +795,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>4387</t>
+          <t>4493</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>1433</t>
+          <t>1407</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>10294</t>
+          <t>10737</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>0,47%</t>
+          <t>0,44%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>0,15%</t>
+          <t>0,14%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>1,1%</t>
+          <t>1,05%</t>
         </is>
       </c>
     </row>
@@ -838,27 +838,27 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>497349</t>
+          <t>540099</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>492062</t>
+          <t>535375</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>498482</t>
+          <t>541263</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>99,77%</t>
+          <t>99,79%</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>98,71%</t>
+          <t>98,91%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -873,32 +873,32 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>437671</t>
+          <t>477997</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>432247</t>
+          <t>472441</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>439859</t>
+          <t>480494</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>99,26%</t>
+          <t>99,31%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>98,03%</t>
+          <t>98,15%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>99,76%</t>
+          <t>99,83%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -908,32 +908,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>935020</t>
+          <t>1018097</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>929113</t>
+          <t>1011853</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>937974</t>
+          <t>1021183</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>99,53%</t>
+          <t>99,56%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>98,9%</t>
+          <t>98,95%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>99,85%</t>
+          <t>99,86%</t>
         </is>
       </c>
     </row>
@@ -951,17 +951,17 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>498482</t>
+          <t>541263</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>498482</t>
+          <t>541263</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>498482</t>
+          <t>541263</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -986,17 +986,17 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>440925</t>
+          <t>481327</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>440925</t>
+          <t>481327</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>440925</t>
+          <t>481327</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1021,17 +1021,17 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>939407</t>
+          <t>1022590</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>939407</t>
+          <t>1022590</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>939407</t>
+          <t>1022590</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1068,7 +1068,7 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>1156</t>
+          <t>1181</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
@@ -1078,12 +1078,12 @@
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>6580</t>
+          <t>5889</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>0,26%</t>
+          <t>0,25%</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
@@ -1093,7 +1093,7 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>1,47%</t>
+          <t>1,23%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1103,32 +1103,32 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>3139</t>
+          <t>3506</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>1027</t>
+          <t>1360</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>7343</t>
+          <t>8181</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>0,83%</t>
+          <t>0,84%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>0,27%</t>
+          <t>0,33%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>1,94%</t>
+          <t>1,96%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1138,17 +1138,17 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>4295</t>
+          <t>4686</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>1394</t>
+          <t>1744</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>9925</t>
+          <t>9606</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1158,12 +1158,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>0,17%</t>
+          <t>0,19%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>1,2%</t>
+          <t>1,07%</t>
         </is>
       </c>
     </row>
@@ -1181,27 +1181,27 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>447262</t>
+          <t>478151</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>441838</t>
+          <t>473443</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>448418</t>
+          <t>479332</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>99,74%</t>
+          <t>99,75%</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>98,53%</t>
+          <t>98,77%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -1216,32 +1216,32 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>374467</t>
+          <t>414414</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>370263</t>
+          <t>409739</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>376579</t>
+          <t>416560</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>99,17%</t>
+          <t>99,16%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>98,06%</t>
+          <t>98,04%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>99,73%</t>
+          <t>99,67%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1251,17 +1251,17 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>821728</t>
+          <t>892567</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>816098</t>
+          <t>887647</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>824629</t>
+          <t>895509</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1271,12 +1271,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>98,8%</t>
+          <t>98,93%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>99,83%</t>
+          <t>99,81%</t>
         </is>
       </c>
     </row>
@@ -1294,17 +1294,17 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>448418</t>
+          <t>479332</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>448418</t>
+          <t>479332</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>448418</t>
+          <t>479332</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -1329,17 +1329,17 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>377606</t>
+          <t>417920</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>377606</t>
+          <t>417920</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>377606</t>
+          <t>417920</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1364,17 +1364,17 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>826023</t>
+          <t>897253</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>826023</t>
+          <t>897253</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>826023</t>
+          <t>897253</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -1411,7 +1411,7 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>2503</t>
+          <t>2460</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
@@ -1421,12 +1421,12 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>9285</t>
+          <t>8272</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>0,38%</t>
+          <t>0,53%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
@@ -1436,7 +1436,7 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>1,41%</t>
+          <t>1,78%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1446,32 +1446,32 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>3059</t>
+          <t>3397</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>1105</t>
+          <t>739</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>8016</t>
+          <t>9010</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>1,85%</t>
+          <t>1,84%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>0,67%</t>
+          <t>0,4%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>4,86%</t>
+          <t>4,87%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1481,32 +1481,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>5562</t>
+          <t>5858</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>1340</t>
+          <t>2008</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>13816</t>
+          <t>13080</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>0,67%</t>
+          <t>0,9%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>0,16%</t>
+          <t>0,31%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>1,67%</t>
+          <t>2,02%</t>
         </is>
       </c>
     </row>
@@ -1524,27 +1524,27 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>658226</t>
+          <t>461405</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>651444</t>
+          <t>455593</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>660729</t>
+          <t>463865</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>99,62%</t>
+          <t>99,47%</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>98,59%</t>
+          <t>98,22%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
@@ -1559,32 +1559,32 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>161909</t>
+          <t>181436</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>156952</t>
+          <t>175823</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>163863</t>
+          <t>184094</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>98,15%</t>
+          <t>98,16%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>95,14%</t>
+          <t>95,13%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>99,33%</t>
+          <t>99,6%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1594,32 +1594,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>820135</t>
+          <t>642840</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>811881</t>
+          <t>635618</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>824357</t>
+          <t>646690</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>99,33%</t>
+          <t>99,1%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>98,33%</t>
+          <t>97,98%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>99,84%</t>
+          <t>99,69%</t>
         </is>
       </c>
     </row>
@@ -1637,17 +1637,17 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>660729</t>
+          <t>463865</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>660729</t>
+          <t>463865</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>660729</t>
+          <t>463865</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1672,17 +1672,17 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>164968</t>
+          <t>184833</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>164968</t>
+          <t>184833</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>164968</t>
+          <t>184833</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1707,17 +1707,17 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>825697</t>
+          <t>648698</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>825697</t>
+          <t>648698</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>825697</t>
+          <t>648698</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1754,7 +1754,7 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>711</t>
+          <t>955</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
@@ -1764,12 +1764,12 @@
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>3487</t>
+          <t>4789</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>0,07%</t>
+          <t>0,09%</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
@@ -1779,7 +1779,7 @@
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>0,35%</t>
+          <t>0,44%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1789,32 +1789,32 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>1394</t>
+          <t>2467</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>161</t>
+          <t>681</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>4523</t>
+          <t>6615</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>0,15%</t>
+          <t>0,29%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>0,02%</t>
+          <t>0,08%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>0,47%</t>
+          <t>0,79%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1824,32 +1824,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>2105</t>
+          <t>3422</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>587</t>
+          <t>1075</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>6175</t>
+          <t>8947</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>0,11%</t>
+          <t>0,18%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>0,03%</t>
+          <t>0,06%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>0,32%</t>
+          <t>0,46%</t>
         </is>
       </c>
     </row>
@@ -1867,27 +1867,27 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>997440</t>
+          <t>1094744</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>994664</t>
+          <t>1090910</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>998151</t>
+          <t>1095699</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>99,93%</t>
+          <t>99,91%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>99,65%</t>
+          <t>99,56%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -1902,32 +1902,32 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>957475</t>
+          <t>834323</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>954346</t>
+          <t>830175</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>958708</t>
+          <t>836109</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>99,85%</t>
+          <t>99,71%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>99,53%</t>
+          <t>99,21%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>99,98%</t>
+          <t>99,92%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1937,32 +1937,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>1954915</t>
+          <t>1929067</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1950845</t>
+          <t>1923542</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1956433</t>
+          <t>1931414</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>99,89%</t>
+          <t>99,82%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>99,68%</t>
+          <t>99,54%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>99,97%</t>
+          <t>99,94%</t>
         </is>
       </c>
     </row>
@@ -1980,17 +1980,17 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>998151</t>
+          <t>1095699</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>998151</t>
+          <t>1095699</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>998151</t>
+          <t>1095699</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -2015,17 +2015,17 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>958869</t>
+          <t>836790</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>958869</t>
+          <t>836790</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>958869</t>
+          <t>836790</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2050,17 +2050,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>1957020</t>
+          <t>1932489</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>1957020</t>
+          <t>1932489</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>1957020</t>
+          <t>1932489</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -2097,7 +2097,7 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>1321</t>
+          <t>1353</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
@@ -2107,12 +2107,12 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>8260</t>
+          <t>6850</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>0,3%</t>
+          <t>0,27%</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
@@ -2122,7 +2122,7 @@
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>1,88%</t>
+          <t>1,34%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2132,67 +2132,67 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>3808</t>
+          <t>4725</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>1657</t>
+          <t>2010</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>7589</t>
+          <t>9701</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
+          <t>0,6%</t>
+        </is>
+      </c>
+      <c r="O16" s="2" t="inlineStr">
+        <is>
+          <t>0,25%</t>
+        </is>
+      </c>
+      <c r="P16" s="2" t="inlineStr">
+        <is>
+          <t>1,22%</t>
+        </is>
+      </c>
+      <c r="Q16" s="2" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="R16" s="2" t="inlineStr">
+        <is>
+          <t>6078</t>
+        </is>
+      </c>
+      <c r="S16" s="2" t="inlineStr">
+        <is>
+          <t>2753</t>
+        </is>
+      </c>
+      <c r="T16" s="2" t="inlineStr">
+        <is>
+          <t>12873</t>
+        </is>
+      </c>
+      <c r="U16" s="2" t="inlineStr">
+        <is>
           <t>0,47%</t>
         </is>
       </c>
-      <c r="O16" s="2" t="inlineStr">
-        <is>
-          <t>0,2%</t>
-        </is>
-      </c>
-      <c r="P16" s="2" t="inlineStr">
-        <is>
-          <t>0,93%</t>
-        </is>
-      </c>
-      <c r="Q16" s="2" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="R16" s="2" t="inlineStr">
-        <is>
-          <t>5129</t>
-        </is>
-      </c>
-      <c r="S16" s="2" t="inlineStr">
-        <is>
-          <t>2366</t>
-        </is>
-      </c>
-      <c r="T16" s="2" t="inlineStr">
-        <is>
-          <t>10804</t>
-        </is>
-      </c>
-      <c r="U16" s="2" t="inlineStr">
-        <is>
-          <t>0,41%</t>
-        </is>
-      </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>0,19%</t>
+          <t>0,21%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>0,86%</t>
+          <t>0,99%</t>
         </is>
       </c>
     </row>
@@ -2210,27 +2210,27 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>437531</t>
+          <t>508495</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>430592</t>
+          <t>502998</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>438852</t>
+          <t>509848</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>99,7%</t>
+          <t>99,73%</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>98,12%</t>
+          <t>98,66%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
@@ -2245,67 +2245,67 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>810173</t>
+          <t>788780</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>806392</t>
+          <t>783804</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>812324</t>
+          <t>791495</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
+          <t>99,4%</t>
+        </is>
+      </c>
+      <c r="O17" s="2" t="inlineStr">
+        <is>
+          <t>98,78%</t>
+        </is>
+      </c>
+      <c r="P17" s="2" t="inlineStr">
+        <is>
+          <t>99,75%</t>
+        </is>
+      </c>
+      <c r="Q17" s="2" t="inlineStr">
+        <is>
+          <t>1723</t>
+        </is>
+      </c>
+      <c r="R17" s="2" t="inlineStr">
+        <is>
+          <t>1297275</t>
+        </is>
+      </c>
+      <c r="S17" s="2" t="inlineStr">
+        <is>
+          <t>1290480</t>
+        </is>
+      </c>
+      <c r="T17" s="2" t="inlineStr">
+        <is>
+          <t>1300600</t>
+        </is>
+      </c>
+      <c r="U17" s="2" t="inlineStr">
+        <is>
           <t>99,53%</t>
         </is>
       </c>
-      <c r="O17" s="2" t="inlineStr">
-        <is>
-          <t>99,07%</t>
-        </is>
-      </c>
-      <c r="P17" s="2" t="inlineStr">
-        <is>
-          <t>99,8%</t>
-        </is>
-      </c>
-      <c r="Q17" s="2" t="inlineStr">
-        <is>
-          <t>1723</t>
-        </is>
-      </c>
-      <c r="R17" s="2" t="inlineStr">
-        <is>
-          <t>1247704</t>
-        </is>
-      </c>
-      <c r="S17" s="2" t="inlineStr">
-        <is>
-          <t>1242029</t>
-        </is>
-      </c>
-      <c r="T17" s="2" t="inlineStr">
-        <is>
-          <t>1250467</t>
-        </is>
-      </c>
-      <c r="U17" s="2" t="inlineStr">
-        <is>
-          <t>99,59%</t>
-        </is>
-      </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>99,14%</t>
+          <t>99,01%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>99,81%</t>
+          <t>99,79%</t>
         </is>
       </c>
     </row>
@@ -2323,17 +2323,17 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>438852</t>
+          <t>509848</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>438852</t>
+          <t>509848</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>438852</t>
+          <t>509848</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2358,17 +2358,17 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>813981</t>
+          <t>793505</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>813981</t>
+          <t>793505</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>813981</t>
+          <t>793505</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2393,17 +2393,17 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>1252833</t>
+          <t>1303353</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>1252833</t>
+          <t>1303353</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>1252833</t>
+          <t>1303353</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2425,7 +2425,7 @@
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B19" s="3" t="inlineStr">
@@ -2440,7 +2440,7 @@
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>1643</t>
+          <t>1842</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
@@ -2450,12 +2450,12 @@
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>8864</t>
+          <t>9820</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>0,7%</t>
+          <t>0,82%</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
@@ -2465,7 +2465,7 @@
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>3,8%</t>
+          <t>4,35%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2475,32 +2475,32 @@
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>5208</t>
+          <t>5559</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>2513</t>
+          <t>2466</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>11013</t>
+          <t>10635</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>0,7%</t>
+          <t>0,68%</t>
         </is>
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>0,34%</t>
+          <t>0,3%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>1,48%</t>
+          <t>1,3%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2510,32 +2510,32 @@
       </c>
       <c r="R19" s="2" t="inlineStr">
         <is>
-          <t>6851</t>
+          <t>7401</t>
         </is>
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>3398</t>
+          <t>3430</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>14620</t>
+          <t>14596</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
         <is>
-          <t>0,7%</t>
+          <t>0,71%</t>
         </is>
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>0,35%</t>
+          <t>0,33%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>1,5%</t>
+          <t>1,4%</t>
         </is>
       </c>
     </row>
@@ -2553,27 +2553,27 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>231569</t>
+          <t>223945</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>224348</t>
+          <t>215967</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>233212</t>
+          <t>225787</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>99,3%</t>
+          <t>99,18%</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>96,2%</t>
+          <t>95,65%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
@@ -2588,32 +2588,32 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>738702</t>
+          <t>813183</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>732897</t>
+          <t>808107</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>741397</t>
+          <t>816276</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>99,3%</t>
+          <t>99,32%</t>
         </is>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>98,52%</t>
+          <t>98,7%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>99,66%</t>
+          <t>99,7%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2623,32 +2623,32 @@
       </c>
       <c r="R20" s="2" t="inlineStr">
         <is>
-          <t>970271</t>
+          <t>1037128</t>
         </is>
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>962502</t>
+          <t>1029933</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>973724</t>
+          <t>1041099</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
         <is>
-          <t>99,3%</t>
+          <t>99,29%</t>
         </is>
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>98,5%</t>
+          <t>98,6%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>99,65%</t>
+          <t>99,67%</t>
         </is>
       </c>
     </row>
@@ -2666,17 +2666,17 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>233212</t>
+          <t>225787</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>233212</t>
+          <t>225787</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>233212</t>
+          <t>225787</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -2701,17 +2701,17 @@
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>743910</t>
+          <t>818742</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>743910</t>
+          <t>818742</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>743910</t>
+          <t>818742</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -2736,17 +2736,17 @@
       </c>
       <c r="R21" s="2" t="inlineStr">
         <is>
-          <t>977122</t>
+          <t>1044529</t>
         </is>
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>977122</t>
+          <t>1044529</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>977122</t>
+          <t>1044529</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -2783,32 +2783,32 @@
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>8468</t>
+          <t>8954</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>3404</t>
+          <t>3677</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>18031</t>
+          <t>20191</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>0,26%</t>
+          <t>0,27%</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>0,1%</t>
+          <t>0,11%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>0,55%</t>
+          <t>0,61%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2818,32 +2818,32 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>19862</t>
+          <t>22984</t>
         </is>
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>12775</t>
+          <t>15740</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>28695</t>
+          <t>32751</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
-          <t>0,57%</t>
+          <t>0,65%</t>
         </is>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>0,36%</t>
+          <t>0,45%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>0,82%</t>
+          <t>0,93%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2853,32 +2853,32 @@
       </c>
       <c r="R22" s="2" t="inlineStr">
         <is>
-          <t>28329</t>
+          <t>31938</t>
         </is>
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>19801</t>
+          <t>22622</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>40139</t>
+          <t>44366</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
         <is>
-          <t>0,42%</t>
+          <t>0,47%</t>
         </is>
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>0,29%</t>
+          <t>0,33%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>0,59%</t>
+          <t>0,65%</t>
         </is>
       </c>
     </row>
@@ -2896,32 +2896,32 @@
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>3269375</t>
+          <t>3306841</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>3259812</t>
+          <t>3295604</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>3274439</t>
+          <t>3312118</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>99,74%</t>
+          <t>99,73%</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>99,45%</t>
+          <t>99,39%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>99,9%</t>
+          <t>99,89%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2931,32 +2931,32 @@
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>3480397</t>
+          <t>3510134</t>
         </is>
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>3471564</t>
+          <t>3500367</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>3487484</t>
+          <t>3517378</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>99,43%</t>
+          <t>99,35%</t>
         </is>
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>99,18%</t>
+          <t>99,07%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>99,64%</t>
+          <t>99,55%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2966,32 +2966,32 @@
       </c>
       <c r="R23" s="2" t="inlineStr">
         <is>
-          <t>6749773</t>
+          <t>6816975</t>
         </is>
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>6737963</t>
+          <t>6804547</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>6758301</t>
+          <t>6826291</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
         <is>
-          <t>99,58%</t>
+          <t>99,53%</t>
         </is>
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>99,41%</t>
+          <t>99,35%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>99,71%</t>
+          <t>99,67%</t>
         </is>
       </c>
     </row>
@@ -3009,17 +3009,17 @@
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>3277843</t>
+          <t>3315795</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>3277843</t>
+          <t>3315795</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>3277843</t>
+          <t>3315795</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -3044,17 +3044,17 @@
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>3500259</t>
+          <t>3533118</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>3500259</t>
+          <t>3533118</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>3500259</t>
+          <t>3533118</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -3079,17 +3079,17 @@
       </c>
       <c r="R24" s="2" t="inlineStr">
         <is>
-          <t>6778102</t>
+          <t>6848913</t>
         </is>
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>6778102</t>
+          <t>6848913</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>6778102</t>
+          <t>6848913</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
